--- a/Kolkata-March-2026.xlsx
+++ b/Kolkata-March-2026.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="39">
   <si>
     <t>Sr. No</t>
   </si>
@@ -115,19 +115,13 @@
     <t>WB04J4973</t>
   </si>
   <si>
-    <t>Crysta</t>
-  </si>
-  <si>
-    <t>Dzire</t>
-  </si>
-  <si>
-    <t>Tours</t>
-  </si>
-  <si>
-    <t>EC3</t>
-  </si>
-  <si>
-    <t>-</t>
+    <t>CRYSTA</t>
+  </si>
+  <si>
+    <t>DZIRE</t>
+  </si>
+  <si>
+    <t>CITROEN</t>
   </si>
   <si>
     <t>15/03/2023</t>
@@ -600,8 +594,8 @@
       <c r="F2" t="s">
         <v>33</v>
       </c>
-      <c r="G2" t="s">
-        <v>37</v>
+      <c r="G2" s="2">
+        <v>44206</v>
       </c>
       <c r="H2">
         <v>69307</v>
@@ -681,7 +675,7 @@
         <v>33</v>
       </c>
       <c r="G3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H3">
         <v>121694</v>
@@ -838,10 +832,10 @@
         <v>31</v>
       </c>
       <c r="F5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H5">
         <v>30971</v>
@@ -918,10 +912,10 @@
         <v>32</v>
       </c>
       <c r="F6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="H6">
         <v>51889</v>
